--- a/data/planilla-ejemplo.xlsx
+++ b/data/planilla-ejemplo.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="568">
   <si>
     <t>id</t>
   </si>
@@ -264,57 +264,60 @@
     <t>06/12/2026</t>
   </si>
   <si>
+    <t>CU2</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>CU3</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>CU4</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>SE1</t>
+  </si>
+  <si>
+    <t>semis</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>12/12/2026</t>
+  </si>
+  <si>
+    <t>SE2</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>en juego</t>
+  </si>
+  <si>
+    <t>FIN</t>
+  </si>
+  <si>
+    <t>final</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
     <t>programado</t>
   </si>
   <si>
-    <t>CU2</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>CU3</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>CU4</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>SE1</t>
-  </si>
-  <si>
-    <t>semis</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>12/12/2026</t>
-  </si>
-  <si>
-    <t>SE2</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>FIN</t>
-  </si>
-  <si>
-    <t>final</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
     <t>partido_id</t>
   </si>
   <si>
@@ -645,6 +648,36 @@
     <t>1996-04</t>
   </si>
   <si>
+    <t>2003-05</t>
+  </si>
+  <si>
+    <t>2003-04</t>
+  </si>
+  <si>
+    <t>2002-14</t>
+  </si>
+  <si>
+    <t>1993-11</t>
+  </si>
+  <si>
+    <t>2008-10</t>
+  </si>
+  <si>
+    <t>2008-07</t>
+  </si>
+  <si>
+    <t>1993-04</t>
+  </si>
+  <si>
+    <t>2008-02</t>
+  </si>
+  <si>
+    <t>2001-03</t>
+  </si>
+  <si>
+    <t>2007-04</t>
+  </si>
+  <si>
     <t>número</t>
   </si>
   <si>
@@ -681,9 +714,6 @@
     <t>Defensor</t>
   </si>
   <si>
-    <t>1993-04</t>
-  </si>
-  <si>
     <t>Manuel Echeverría</t>
   </si>
   <si>
@@ -708,9 +738,6 @@
     <t>Facundo Álvarez</t>
   </si>
   <si>
-    <t>1993-11</t>
-  </si>
-  <si>
     <t>Esteban Olivera</t>
   </si>
   <si>
@@ -1206,9 +1233,6 @@
     <t>Benjamín Sosa</t>
   </si>
   <si>
-    <t>2001-03</t>
-  </si>
-  <si>
     <t>Tobías Castro</t>
   </si>
   <si>
@@ -1311,9 +1335,6 @@
     <t>Patricio Fernández</t>
   </si>
   <si>
-    <t>2002-14</t>
-  </si>
-  <si>
     <t>Federico Vázquez</t>
   </si>
   <si>
@@ -1335,15 +1356,9 @@
     <t>Juan Cruz García</t>
   </si>
   <si>
-    <t>2003-04</t>
-  </si>
-  <si>
     <t>Ramiro Etchegaray</t>
   </si>
   <si>
-    <t>2003-05</t>
-  </si>
-  <si>
     <t>Joaquín González</t>
   </si>
   <si>
@@ -1581,9 +1596,6 @@
     <t>Sebastián Ferrari</t>
   </si>
   <si>
-    <t>2007-04</t>
-  </si>
-  <si>
     <t>Santiago Olivera</t>
   </si>
   <si>
@@ -1626,9 +1638,6 @@
     <t>Felipe Benítez</t>
   </si>
   <si>
-    <t>2008-02</t>
-  </si>
-  <si>
     <t>Santiago Cabrera</t>
   </si>
   <si>
@@ -1653,9 +1662,6 @@
     <t>Maximiliano Basavilbaso</t>
   </si>
   <si>
-    <t>2008-07</t>
-  </si>
-  <si>
     <t>Juan Cruz Cabrera</t>
   </si>
   <si>
@@ -1666,9 +1672,6 @@
   </si>
   <si>
     <t>Bautista Morales</t>
-  </si>
-  <si>
-    <t>2008-10</t>
   </si>
   <si>
     <t>Esteban Arias</t>
@@ -3302,19 +3305,19 @@
         <v>64</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>81</v>
@@ -3331,19 +3334,25 @@
         <v>64</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>82</v>
+        <v>43</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>81</v>
@@ -3360,19 +3369,25 @@
         <v>64</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>82</v>
+        <v>43</v>
+      </c>
+      <c r="M28">
+        <v>5</v>
+      </c>
+      <c r="N28">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>81</v>
@@ -3389,22 +3404,22 @@
         <v>46</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>40</v>
@@ -3418,22 +3433,28 @@
         <v>57</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>82</v>
+        <v>43</v>
+      </c>
+      <c r="M30">
+        <v>5</v>
+      </c>
+      <c r="N30">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>40</v>
@@ -3447,7 +3468,7 @@
         <v>54</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -3462,7 +3483,7 @@
         <v>97</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>98</v>
@@ -3476,7 +3497,7 @@
         <v>57</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -7387,19 +7408,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -7407,13 +7428,13 @@
         <v>38</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -7424,13 +7445,13 @@
         <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E3">
         <v>9</v>
@@ -7441,13 +7462,13 @@
         <v>38</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4">
         <v>29</v>
@@ -7458,13 +7479,13 @@
         <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>19</v>
@@ -7475,13 +7496,13 @@
         <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E6">
         <v>33</v>
@@ -7492,13 +7513,13 @@
         <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E7">
         <v>40</v>
@@ -7509,13 +7530,13 @@
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E8">
         <v>14</v>
@@ -7526,13 +7547,13 @@
         <v>47</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E9">
         <v>30</v>
@@ -7543,13 +7564,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E10">
         <v>46</v>
@@ -7560,13 +7581,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E11">
         <v>49</v>
@@ -7577,13 +7598,13 @@
         <v>49</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -7594,13 +7615,13 @@
         <v>49</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -7611,13 +7632,13 @@
         <v>49</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E14">
         <v>11</v>
@@ -7628,13 +7649,13 @@
         <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E15">
         <v>11</v>
@@ -7645,13 +7666,13 @@
         <v>49</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E16">
         <v>13</v>
@@ -7662,13 +7683,13 @@
         <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E17">
         <v>14</v>
@@ -7679,13 +7700,13 @@
         <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E18">
         <v>14</v>
@@ -7696,13 +7717,13 @@
         <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E19">
         <v>37</v>
@@ -7713,13 +7734,13 @@
         <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E20">
         <v>37</v>
@@ -7730,13 +7751,13 @@
         <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E21">
         <v>39</v>
@@ -7747,13 +7768,13 @@
         <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E22">
         <v>44</v>
@@ -7764,13 +7785,13 @@
         <v>51</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E23">
         <v>13</v>
@@ -7781,13 +7802,13 @@
         <v>51</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E24">
         <v>20</v>
@@ -7798,13 +7819,13 @@
         <v>51</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E25">
         <v>21</v>
@@ -7815,13 +7836,13 @@
         <v>51</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E26">
         <v>27</v>
@@ -7832,13 +7853,13 @@
         <v>51</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E27">
         <v>33</v>
@@ -7849,13 +7870,13 @@
         <v>51</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E28">
         <v>41</v>
@@ -7866,13 +7887,13 @@
         <v>51</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E29">
         <v>48</v>
@@ -7883,13 +7904,13 @@
         <v>53</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E30">
         <v>13</v>
@@ -7900,13 +7921,13 @@
         <v>53</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E31">
         <v>24</v>
@@ -7917,13 +7938,13 @@
         <v>53</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E32">
         <v>28</v>
@@ -7934,13 +7955,13 @@
         <v>53</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E33">
         <v>29</v>
@@ -7951,13 +7972,13 @@
         <v>53</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E34">
         <v>40</v>
@@ -7968,13 +7989,13 @@
         <v>53</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E35">
         <v>42</v>
@@ -7985,13 +8006,13 @@
         <v>53</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E36">
         <v>45</v>
@@ -8002,13 +8023,13 @@
         <v>53</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E37">
         <v>45</v>
@@ -8019,13 +8040,13 @@
         <v>55</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E38">
         <v>5</v>
@@ -8036,13 +8057,13 @@
         <v>55</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E39">
         <v>7</v>
@@ -8053,13 +8074,13 @@
         <v>55</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E40">
         <v>21</v>
@@ -8070,13 +8091,13 @@
         <v>55</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E41">
         <v>47</v>
@@ -8087,13 +8108,13 @@
         <v>56</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E42">
         <v>11</v>
@@ -8104,13 +8125,13 @@
         <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E43">
         <v>21</v>
@@ -8121,13 +8142,13 @@
         <v>56</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E44">
         <v>37</v>
@@ -8138,13 +8159,13 @@
         <v>56</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E45">
         <v>45</v>
@@ -8155,13 +8176,13 @@
         <v>58</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E46">
         <v>15</v>
@@ -8172,13 +8193,13 @@
         <v>58</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E47">
         <v>17</v>
@@ -8189,13 +8210,13 @@
         <v>58</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E48">
         <v>36</v>
@@ -8206,13 +8227,13 @@
         <v>60</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E49">
         <v>11</v>
@@ -8223,13 +8244,13 @@
         <v>60</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E50">
         <v>15</v>
@@ -8240,13 +8261,13 @@
         <v>60</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E51">
         <v>17</v>
@@ -8257,13 +8278,13 @@
         <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E52">
         <v>18</v>
@@ -8274,13 +8295,13 @@
         <v>60</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E53">
         <v>21</v>
@@ -8291,13 +8312,13 @@
         <v>60</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E54">
         <v>27</v>
@@ -8308,13 +8329,13 @@
         <v>60</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E55">
         <v>32</v>
@@ -8325,13 +8346,13 @@
         <v>60</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E56">
         <v>33</v>
@@ -8342,13 +8363,13 @@
         <v>60</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E57">
         <v>35</v>
@@ -8359,13 +8380,13 @@
         <v>60</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E58">
         <v>41</v>
@@ -8376,13 +8397,13 @@
         <v>60</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E59">
         <v>48</v>
@@ -8393,13 +8414,13 @@
         <v>61</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E60">
         <v>4</v>
@@ -8410,13 +8431,13 @@
         <v>61</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E61">
         <v>6</v>
@@ -8427,13 +8448,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E62">
         <v>11</v>
@@ -8444,13 +8465,13 @@
         <v>61</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E63">
         <v>21</v>
@@ -8461,13 +8482,13 @@
         <v>61</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E64">
         <v>26</v>
@@ -8478,13 +8499,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E65">
         <v>29</v>
@@ -8495,13 +8516,13 @@
         <v>61</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E66">
         <v>29</v>
@@ -8512,13 +8533,13 @@
         <v>61</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E67">
         <v>33</v>
@@ -8529,13 +8550,13 @@
         <v>63</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E68">
         <v>9</v>
@@ -8546,13 +8567,13 @@
         <v>63</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E69">
         <v>11</v>
@@ -8563,13 +8584,13 @@
         <v>63</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E70">
         <v>14</v>
@@ -8580,13 +8601,13 @@
         <v>63</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E71">
         <v>22</v>
@@ -8597,13 +8618,13 @@
         <v>63</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E72">
         <v>29</v>
@@ -8614,13 +8635,13 @@
         <v>63</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E73">
         <v>38</v>
@@ -8631,13 +8652,13 @@
         <v>63</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E74">
         <v>39</v>
@@ -8648,13 +8669,13 @@
         <v>63</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E75">
         <v>45</v>
@@ -8665,13 +8686,13 @@
         <v>63</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E76">
         <v>48</v>
@@ -8682,13 +8703,13 @@
         <v>65</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E77">
         <v>9</v>
@@ -8699,13 +8720,13 @@
         <v>65</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E78">
         <v>11</v>
@@ -8716,13 +8737,13 @@
         <v>65</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E79">
         <v>12</v>
@@ -8733,13 +8754,13 @@
         <v>65</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E80">
         <v>19</v>
@@ -8750,13 +8771,13 @@
         <v>65</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E81">
         <v>23</v>
@@ -8767,13 +8788,13 @@
         <v>65</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E82">
         <v>27</v>
@@ -8784,13 +8805,13 @@
         <v>65</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E83">
         <v>43</v>
@@ -8801,13 +8822,13 @@
         <v>65</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E84">
         <v>49</v>
@@ -8818,13 +8839,13 @@
         <v>65</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E85">
         <v>50</v>
@@ -8835,13 +8856,13 @@
         <v>66</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E86">
         <v>8</v>
@@ -8852,13 +8873,13 @@
         <v>66</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E87">
         <v>10</v>
@@ -8869,13 +8890,13 @@
         <v>66</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E88">
         <v>10</v>
@@ -8886,13 +8907,13 @@
         <v>67</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E89">
         <v>21</v>
@@ -8903,13 +8924,13 @@
         <v>67</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E90">
         <v>22</v>
@@ -8920,13 +8941,13 @@
         <v>68</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E91">
         <v>12</v>
@@ -8937,13 +8958,13 @@
         <v>68</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E92">
         <v>23</v>
@@ -8954,13 +8975,13 @@
         <v>68</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E93">
         <v>27</v>
@@ -8971,13 +8992,13 @@
         <v>68</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E94">
         <v>29</v>
@@ -8988,13 +9009,13 @@
         <v>68</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E95">
         <v>43</v>
@@ -9005,13 +9026,13 @@
         <v>69</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E96">
         <v>15</v>
@@ -9022,13 +9043,13 @@
         <v>69</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E97">
         <v>25</v>
@@ -9039,13 +9060,13 @@
         <v>69</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E98">
         <v>26</v>
@@ -9056,13 +9077,13 @@
         <v>69</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E99">
         <v>35</v>
@@ -9073,13 +9094,13 @@
         <v>69</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E100">
         <v>36</v>
@@ -9090,13 +9111,13 @@
         <v>71</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E101">
         <v>14</v>
@@ -9107,13 +9128,13 @@
         <v>71</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E102">
         <v>23</v>
@@ -9124,13 +9145,13 @@
         <v>71</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E103">
         <v>24</v>
@@ -9141,13 +9162,13 @@
         <v>71</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E104">
         <v>38</v>
@@ -9158,13 +9179,13 @@
         <v>72</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E105">
         <v>4</v>
@@ -9175,13 +9196,13 @@
         <v>72</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E106">
         <v>13</v>
@@ -9192,13 +9213,13 @@
         <v>72</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E107">
         <v>42</v>
@@ -9209,13 +9230,13 @@
         <v>72</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E108">
         <v>46</v>
@@ -9226,13 +9247,13 @@
         <v>72</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E109">
         <v>50</v>
@@ -9243,13 +9264,13 @@
         <v>73</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E110">
         <v>5</v>
@@ -9260,13 +9281,13 @@
         <v>73</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E111">
         <v>5</v>
@@ -9277,13 +9298,13 @@
         <v>73</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E112">
         <v>7</v>
@@ -9294,13 +9315,13 @@
         <v>73</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E113">
         <v>7</v>
@@ -9311,13 +9332,13 @@
         <v>73</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -9328,13 +9349,13 @@
         <v>73</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E115">
         <v>25</v>
@@ -9345,13 +9366,13 @@
         <v>73</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E116">
         <v>32</v>
@@ -9362,13 +9383,13 @@
         <v>73</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E117">
         <v>36</v>
@@ -9379,13 +9400,13 @@
         <v>74</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -9396,13 +9417,13 @@
         <v>74</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E119">
         <v>10</v>
@@ -9413,13 +9434,13 @@
         <v>74</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E120">
         <v>37</v>
@@ -9430,13 +9451,13 @@
         <v>74</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E121">
         <v>46</v>
@@ -9447,13 +9468,13 @@
         <v>74</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E122">
         <v>50</v>
@@ -9464,13 +9485,13 @@
         <v>75</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E123">
         <v>19</v>
@@ -9481,13 +9502,13 @@
         <v>75</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E124">
         <v>22</v>
@@ -9498,13 +9519,13 @@
         <v>75</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E125">
         <v>44</v>
@@ -9515,13 +9536,13 @@
         <v>76</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E126">
         <v>15</v>
@@ -9532,13 +9553,13 @@
         <v>76</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E127">
         <v>22</v>
@@ -9549,13 +9570,13 @@
         <v>76</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E128">
         <v>32</v>
@@ -9566,13 +9587,13 @@
         <v>76</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E129">
         <v>44</v>
@@ -9583,13 +9604,13 @@
         <v>76</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E130">
         <v>45</v>
@@ -9600,13 +9621,13 @@
         <v>77</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E131">
         <v>1</v>
@@ -9617,13 +9638,13 @@
         <v>77</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E132">
         <v>11</v>
@@ -9634,13 +9655,13 @@
         <v>77</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E133">
         <v>18</v>
@@ -9651,13 +9672,13 @@
         <v>77</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E134">
         <v>20</v>
@@ -9668,122 +9689,612 @@
         <v>77</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E135">
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B136" s="1"/>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B137" s="1"/>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B138" s="1"/>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B139" s="1"/>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B140" s="1"/>
-    </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B141" s="1"/>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B142" s="1"/>
-    </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B143" s="1"/>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B144" s="1"/>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B145" s="1"/>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B146" s="1"/>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B147" s="1"/>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B148" s="1"/>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B149" s="1"/>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B150" s="1"/>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B151" s="1"/>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B152" s="1"/>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B153" s="1"/>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B154" s="1"/>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B155" s="1"/>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B156" s="1"/>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B157" s="1"/>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B158" s="1"/>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B159" s="1"/>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B160" s="1"/>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B161" s="1"/>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B162" s="1"/>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B163" s="1"/>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B164" s="1"/>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B165" s="1"/>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B166" s="1"/>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B167" s="1"/>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B168" s="1"/>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B169" s="1"/>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B170" s="1"/>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E136">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E137">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E138">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E139">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E140">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E141">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E142">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E143">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E144">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E145">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E146">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E147">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E148">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E149">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E150">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E151">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E152">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E153">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E154">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E156">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E157">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E158">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E159">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E160">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E161">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E162">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E163">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E164">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E166">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E167">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E168">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E169">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E170">
+        <v>20</v>
+      </c>
     </row>
     <row r="171" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B171" s="1"/>
@@ -12307,42 +12818,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2">
@@ -12354,19 +12865,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D3">
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3">
@@ -12378,19 +12889,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D4">
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4">
@@ -12402,19 +12913,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D5">
         <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5">
@@ -12426,19 +12937,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D6">
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6">
@@ -12450,19 +12961,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D7">
         <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7">
@@ -12474,19 +12985,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D8">
         <v>16</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8">
@@ -12498,19 +13009,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D9">
         <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9">
@@ -12522,19 +13033,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D10">
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10">
@@ -12546,19 +13057,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D11">
         <v>13</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11">
@@ -12570,19 +13081,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12">
@@ -12594,19 +13105,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D13">
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13">
@@ -12618,19 +13129,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D14">
         <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14">
@@ -12642,19 +13153,19 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D15">
         <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15">
@@ -12666,19 +13177,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16">
@@ -12690,19 +13201,19 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="D17">
         <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17">
@@ -12714,19 +13225,19 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D18">
         <v>19</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18">
@@ -12738,19 +13249,19 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D19">
         <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19">
@@ -12762,19 +13273,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="D20">
         <v>29</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20">
@@ -12786,19 +13297,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D21">
         <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21">
@@ -12810,19 +13321,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D22">
         <v>5</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22">
@@ -12834,19 +13345,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="D23">
         <v>25</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23">
@@ -12858,19 +13369,19 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D24">
         <v>13</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24">
@@ -12882,19 +13393,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25">
@@ -12906,19 +13417,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D26">
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26">
@@ -12930,19 +13441,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27">
@@ -12954,19 +13465,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28">
@@ -12978,19 +13489,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D29">
         <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29">
@@ -13002,19 +13513,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30">
@@ -13026,19 +13537,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D31">
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31">
@@ -13050,19 +13561,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="D32">
         <v>29</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32">
@@ -13074,19 +13585,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33">
@@ -13098,19 +13609,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="D34">
         <v>13</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34">
@@ -13122,19 +13633,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35">
@@ -13146,19 +13657,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D36">
         <v>6</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36">
@@ -13170,19 +13681,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="D37">
         <v>9</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37">
@@ -13194,19 +13705,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D38">
         <v>27</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38">
@@ -13218,19 +13729,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D39">
         <v>30</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39">
@@ -13242,19 +13753,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D40">
         <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40">
@@ -13266,19 +13777,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="D41">
         <v>19</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41">
@@ -13290,19 +13801,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D42">
         <v>28</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42">
@@ -13314,19 +13825,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D43">
         <v>4</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43">
@@ -13338,19 +13849,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44">
@@ -13362,19 +13873,19 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="D45">
         <v>12</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45">
@@ -13386,19 +13897,19 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D46">
         <v>9</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46">
@@ -13410,19 +13921,19 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D47">
         <v>13</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47">
@@ -13434,19 +13945,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D48">
         <v>5</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48">
@@ -13458,19 +13969,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D49">
         <v>31</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49">
@@ -13482,19 +13993,19 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D50">
         <v>25</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50">
@@ -13506,19 +14017,19 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D51">
         <v>17</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51">
@@ -13530,19 +14041,19 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D52">
         <v>4</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52">
@@ -13554,19 +14065,19 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D53">
         <v>3</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53">
@@ -13578,19 +14089,19 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="D54">
         <v>24</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54">
@@ -13602,19 +14113,19 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D55">
         <v>14</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55">
@@ -13626,19 +14137,19 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="D56">
         <v>16</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56">
@@ -13650,19 +14161,19 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D57">
         <v>26</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57">
@@ -13674,19 +14185,19 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58">
@@ -13698,19 +14209,19 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D59">
         <v>12</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59">
@@ -13722,19 +14233,19 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D60">
         <v>7</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60">
@@ -13746,19 +14257,19 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D61">
         <v>23</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61">
@@ -13770,19 +14281,19 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D62">
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62">
@@ -13794,19 +14305,19 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D63">
         <v>5</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63">
@@ -13818,19 +14329,19 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D64">
         <v>29</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64">
@@ -13842,19 +14353,19 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D65">
         <v>21</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65">
@@ -13866,19 +14377,19 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D66">
         <v>3</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66">
@@ -13890,19 +14401,19 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D67">
         <v>19</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67">
@@ -13914,19 +14425,19 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="D68">
         <v>25</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68">
@@ -13938,19 +14449,19 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="D69">
         <v>4</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69">
@@ -13962,19 +14473,19 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D70">
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70">
@@ -13986,19 +14497,19 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="D71">
         <v>27</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71">
@@ -14010,19 +14521,19 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72">
@@ -14034,19 +14545,19 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="D73">
         <v>12</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73">
@@ -14058,19 +14569,19 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="D74">
         <v>28</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74">
@@ -14082,19 +14593,19 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D75">
         <v>26</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75">
@@ -14106,19 +14617,19 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="D76">
         <v>20</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76">
@@ -14130,19 +14641,19 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D77">
         <v>13</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77">
@@ -14154,19 +14665,19 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D78">
         <v>22</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78">
@@ -14178,19 +14689,19 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="D79">
         <v>23</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79">
@@ -14202,19 +14713,19 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="D80">
         <v>15</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80">
@@ -14226,19 +14737,19 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D81">
         <v>6</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81">
@@ -14250,19 +14761,19 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="D82">
         <v>29</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82">
@@ -14274,19 +14785,19 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D83">
         <v>30</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83">
@@ -14298,19 +14809,19 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="D84">
         <v>8</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84">
@@ -14322,19 +14833,19 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D85">
         <v>5</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85">
@@ -14346,19 +14857,19 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F86" s="1"/>
       <c r="G86">
@@ -14370,19 +14881,19 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="D87">
         <v>12</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F87" s="1"/>
       <c r="G87">
@@ -14394,19 +14905,19 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D88">
         <v>17</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88">
@@ -14418,19 +14929,19 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="D89">
         <v>21</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F89" s="1"/>
       <c r="G89">
@@ -14442,19 +14953,19 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D90">
         <v>8</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F90" s="1"/>
       <c r="G90">
@@ -14466,19 +14977,19 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D91">
         <v>19</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91">
@@ -14490,19 +15001,19 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="D92">
         <v>23</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92">
@@ -14514,19 +15025,19 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="D93">
         <v>22</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93">
@@ -14538,19 +15049,19 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="D94">
         <v>3</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94">
@@ -14562,19 +15073,19 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D95">
         <v>2</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F95" s="1"/>
       <c r="G95">
@@ -14586,19 +15097,19 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="D96">
         <v>20</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F96" s="1"/>
       <c r="G96">
@@ -14610,19 +15121,19 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="D97">
         <v>4</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F97" s="1"/>
       <c r="G97">
@@ -14634,19 +15145,19 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="D98">
         <v>5</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F98" s="1"/>
       <c r="G98">
@@ -14658,19 +15169,19 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="D99">
         <v>9</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99">
@@ -14682,19 +15193,19 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100">
@@ -14706,19 +15217,19 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="D101">
         <v>12</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101">
@@ -14730,19 +15241,19 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="D102">
         <v>19</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102">
@@ -14754,19 +15265,19 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="D103">
         <v>2</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F103" s="1"/>
       <c r="G103">
@@ -14778,19 +15289,19 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="D104">
         <v>16</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F104" s="1"/>
       <c r="G104">
@@ -14802,19 +15313,19 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="D105">
         <v>17</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F105" s="1"/>
       <c r="G105">
@@ -14826,19 +15337,19 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="D106">
         <v>18</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F106" s="1"/>
       <c r="G106">
@@ -14850,19 +15361,19 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="D107">
         <v>20</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107">
@@ -14874,19 +15385,19 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="D108">
         <v>3</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108">
@@ -14898,19 +15409,19 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="D109">
         <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F109" s="1"/>
       <c r="G109">
@@ -14922,19 +15433,19 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="D110">
         <v>5</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F110" s="1"/>
       <c r="G110">
@@ -14946,19 +15457,19 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="D111">
         <v>28</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F111" s="1"/>
       <c r="G111">
@@ -14970,19 +15481,19 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="D112">
         <v>26</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F112" s="1"/>
       <c r="G112">
@@ -14994,19 +15505,19 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="D113">
         <v>21</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F113" s="1"/>
       <c r="G113">
@@ -15018,19 +15529,19 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F114" s="1"/>
       <c r="G114">
@@ -15042,19 +15553,19 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="D115">
         <v>12</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F115" s="1"/>
       <c r="G115">
@@ -15066,19 +15577,19 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>396</v>
+        <v>218</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D116">
         <v>13</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F116" s="1"/>
       <c r="G116">
@@ -15090,19 +15601,19 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D117">
         <v>3</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F117" s="1"/>
       <c r="G117">
@@ -15114,19 +15625,19 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D118">
         <v>22</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F118" s="1"/>
       <c r="G118">
@@ -15138,19 +15649,19 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="D119">
         <v>2</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F119" s="1"/>
       <c r="G119">
@@ -15162,19 +15673,19 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D120">
         <v>21</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120">
@@ -15186,19 +15697,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D121">
         <v>16</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121">
@@ -15210,19 +15721,19 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D122">
         <v>8</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122">
@@ -15234,19 +15745,19 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D123">
         <v>5</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123">
@@ -15258,19 +15769,19 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D124">
         <v>20</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124">
@@ -15282,19 +15793,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D125">
         <v>28</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F125" s="1"/>
       <c r="G125">
@@ -15306,19 +15817,19 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="D126">
         <v>25</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F126" s="1"/>
       <c r="G126">
@@ -15330,19 +15841,19 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D127">
         <v>6</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127">
@@ -15354,19 +15865,19 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F128" s="1"/>
       <c r="G128">
@@ -15378,19 +15889,19 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D129">
         <v>12</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F129" s="1"/>
       <c r="G129">
@@ -15402,19 +15913,19 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="D130">
         <v>25</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F130" s="1"/>
       <c r="G130">
@@ -15426,19 +15937,19 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D131">
         <v>28</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F131" s="1"/>
       <c r="G131">
@@ -15450,19 +15961,19 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="D132">
         <v>14</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F132" s="1"/>
       <c r="G132">
@@ -15474,19 +15985,19 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D133">
         <v>11</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133">
@@ -15498,19 +16009,19 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="D134">
         <v>5</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134">
@@ -15522,19 +16033,19 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="D135">
         <v>3</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135">
@@ -15546,19 +16057,19 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D136">
         <v>9</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136">
@@ -15570,19 +16081,19 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="D137">
         <v>19</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137">
@@ -15594,19 +16105,19 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="D138">
         <v>7</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138">
@@ -15618,19 +16129,19 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="D139">
         <v>31</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139">
@@ -15642,19 +16153,19 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D140">
         <v>13</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F140" s="1"/>
       <c r="G140">
@@ -15666,19 +16177,19 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>431</v>
+        <v>212</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="D141">
         <v>10</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F141" s="1"/>
       <c r="G141">
@@ -15690,19 +16201,19 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F142" s="1"/>
       <c r="G142">
@@ -15714,19 +16225,19 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="D143">
         <v>12</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F143" s="1"/>
       <c r="G143">
@@ -15738,19 +16249,19 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D144">
         <v>8</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F144" s="1"/>
       <c r="G144">
@@ -15762,19 +16273,19 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>439</v>
+        <v>211</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D145">
         <v>6</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F145" s="1"/>
       <c r="G145">
@@ -15786,19 +16297,19 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>441</v>
+        <v>210</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D146">
         <v>10</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F146" s="1"/>
       <c r="G146">
@@ -15810,19 +16321,19 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D147">
         <v>31</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F147" s="1"/>
       <c r="G147">
@@ -15834,19 +16345,19 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D148">
         <v>30</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F148" s="1"/>
       <c r="G148">
@@ -15858,19 +16369,19 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D149">
         <v>19</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F149" s="1"/>
       <c r="G149">
@@ -15882,19 +16393,19 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="D150">
         <v>5</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F150" s="1"/>
       <c r="G150">
@@ -15906,19 +16417,19 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D151">
         <v>16</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151">
@@ -15930,19 +16441,19 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D152">
         <v>24</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F152" s="1"/>
       <c r="G152">
@@ -15954,19 +16465,19 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D153">
         <v>26</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F153" s="1"/>
       <c r="G153">
@@ -15978,19 +16489,19 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D154">
         <v>20</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F154" s="1"/>
       <c r="G154">
@@ -16002,19 +16513,19 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D155">
         <v>15</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155">
@@ -16026,19 +16537,19 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156">
@@ -16050,19 +16561,19 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="D157">
         <v>12</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157">
@@ -16074,19 +16585,19 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D158">
         <v>23</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158">
@@ -16098,19 +16609,19 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D159">
         <v>17</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159">
@@ -16122,19 +16633,19 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D160">
         <v>4</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160">
@@ -16146,19 +16657,19 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="D161">
         <v>7</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161">
@@ -16170,19 +16681,19 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D162">
         <v>21</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162">
@@ -16194,19 +16705,19 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="D163">
         <v>26</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163">
@@ -16218,19 +16729,19 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D164">
         <v>6</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164">
@@ -16242,19 +16753,19 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D165">
         <v>31</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165">
@@ -16266,19 +16777,19 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D166">
         <v>3</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F166" s="1"/>
       <c r="G166">
@@ -16290,19 +16801,19 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D167">
         <v>13</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F167" s="1"/>
       <c r="G167">
@@ -16314,19 +16825,19 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D168">
         <v>24</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F168" s="1"/>
       <c r="G168">
@@ -16338,19 +16849,19 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D169">
         <v>25</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F169" s="1"/>
       <c r="G169">
@@ -16362,19 +16873,19 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D170">
         <v>1</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F170" s="1"/>
       <c r="G170">
@@ -16386,19 +16897,19 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D171">
         <v>12</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F171" s="1"/>
       <c r="G171">
@@ -16410,19 +16921,19 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D172">
         <v>14</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F172" s="1"/>
       <c r="G172">
@@ -16434,19 +16945,19 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D173">
         <v>30</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F173" s="1"/>
       <c r="G173">
@@ -16458,19 +16969,19 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D174">
         <v>11</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F174" s="1"/>
       <c r="G174">
@@ -16482,19 +16993,19 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D175">
         <v>18</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F175" s="1"/>
       <c r="G175">
@@ -16506,19 +17017,19 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D176">
         <v>25</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F176" s="1"/>
       <c r="G176">
@@ -16530,19 +17041,19 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D177">
         <v>23</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F177" s="1"/>
       <c r="G177">
@@ -16554,19 +17065,19 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D178">
         <v>7</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F178" s="1"/>
       <c r="G178">
@@ -16578,19 +17089,19 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="D179">
         <v>8</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F179" s="1"/>
       <c r="G179">
@@ -16602,19 +17113,19 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D180">
         <v>29</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F180" s="1"/>
       <c r="G180">
@@ -16626,19 +17137,19 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D181">
         <v>24</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F181" s="1"/>
       <c r="G181">
@@ -16650,19 +17161,19 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D182">
         <v>16</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F182" s="1"/>
       <c r="G182">
@@ -16674,19 +17185,19 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D183">
         <v>28</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F183" s="1"/>
       <c r="G183">
@@ -16698,19 +17209,19 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D184">
         <v>1</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F184" s="1"/>
       <c r="G184">
@@ -16722,19 +17233,19 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D185">
         <v>12</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F185" s="1"/>
       <c r="G185">
@@ -16746,19 +17257,19 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D186">
         <v>5</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F186" s="1"/>
       <c r="G186">
@@ -16770,19 +17281,19 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D187">
         <v>10</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F187" s="1"/>
       <c r="G187">
@@ -16794,19 +17305,19 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D188">
         <v>7</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F188" s="1"/>
       <c r="G188">
@@ -16818,19 +17329,19 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D189">
         <v>15</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F189" s="1"/>
       <c r="G189">
@@ -16842,19 +17353,19 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D190">
         <v>3</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F190" s="1"/>
       <c r="G190">
@@ -16866,19 +17377,19 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D191">
         <v>19</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F191" s="1"/>
       <c r="G191">
@@ -16890,19 +17401,19 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D192">
         <v>9</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F192" s="1"/>
       <c r="G192">
@@ -16914,19 +17425,19 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D193">
         <v>2</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F193" s="1"/>
       <c r="G193">
@@ -16938,19 +17449,19 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="D194">
         <v>22</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F194" s="1"/>
       <c r="G194">
@@ -16962,19 +17473,19 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D195">
         <v>28</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F195" s="1"/>
       <c r="G195">
@@ -16986,19 +17497,19 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D196">
         <v>30</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F196" s="1"/>
       <c r="G196">
@@ -17010,19 +17521,19 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="D197">
         <v>31</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F197" s="1"/>
       <c r="G197">
@@ -17034,19 +17545,19 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D198">
         <v>1</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F198" s="1"/>
       <c r="G198">
@@ -17058,19 +17569,19 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="D199">
         <v>12</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F199" s="1"/>
       <c r="G199">
@@ -17082,19 +17593,19 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D200">
         <v>8</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F200" s="1"/>
       <c r="G200">
@@ -17106,19 +17617,19 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>521</v>
+        <v>219</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D201">
         <v>3</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F201" s="1"/>
       <c r="G201">
@@ -17130,19 +17641,19 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D202">
         <v>29</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F202" s="1"/>
       <c r="G202">
@@ -17154,19 +17665,19 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D203">
         <v>10</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F203" s="1"/>
       <c r="G203">
@@ -17178,19 +17689,19 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D204">
         <v>14</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F204" s="1"/>
       <c r="G204">
@@ -17202,19 +17713,19 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D205">
         <v>5</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F205" s="1"/>
       <c r="G205">
@@ -17226,19 +17737,19 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D206">
         <v>13</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F206" s="1"/>
       <c r="G206">
@@ -17250,19 +17761,19 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D207">
         <v>25</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F207" s="1"/>
       <c r="G207">
@@ -17274,19 +17785,19 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D208">
         <v>19</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F208" s="1"/>
       <c r="G208">
@@ -17298,19 +17809,19 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D209">
         <v>28</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F209" s="1"/>
       <c r="G209">
@@ -17322,19 +17833,19 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D210">
         <v>6</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F210" s="1"/>
       <c r="G210">
@@ -17346,19 +17857,19 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D211">
         <v>23</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F211" s="1"/>
       <c r="G211">
@@ -17370,19 +17881,19 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D212">
         <v>1</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F212" s="1"/>
       <c r="G212">
@@ -17394,19 +17905,19 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>536</v>
+        <v>217</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D213">
         <v>12</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F213" s="1"/>
       <c r="G213">
@@ -17418,19 +17929,19 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D214">
         <v>22</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F214" s="1"/>
       <c r="G214">
@@ -17442,19 +17953,19 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D215">
         <v>20</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F215" s="1"/>
       <c r="G215">
@@ -17466,19 +17977,19 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D216">
         <v>14</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F216" s="1"/>
       <c r="G216">
@@ -17490,19 +18001,19 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D217">
         <v>15</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F217" s="1"/>
       <c r="G217">
@@ -17514,19 +18025,19 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>545</v>
+        <v>215</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D218">
         <v>30</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F218" s="1"/>
       <c r="G218">
@@ -17538,19 +18049,19 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D219">
         <v>11</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F219" s="1"/>
       <c r="G219">
@@ -17562,19 +18073,19 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D220">
         <v>26</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F220" s="1"/>
       <c r="G220">
@@ -17586,19 +18097,19 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>550</v>
+        <v>214</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D221">
         <v>27</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F221" s="1"/>
       <c r="G221">
@@ -17610,19 +18121,19 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D222">
         <v>17</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F222" s="1"/>
       <c r="G222">
@@ -17634,19 +18145,19 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D223">
         <v>25</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F223" s="1"/>
       <c r="G223">
@@ -17658,19 +18169,19 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D224">
         <v>21</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F224" s="1"/>
       <c r="G224">
@@ -17682,19 +18193,19 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D225">
         <v>2</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F225" s="1"/>
       <c r="G225">
@@ -17720,52 +18231,52 @@
   <sheetData>
     <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>

--- a/data/planilla-ejemplo.xlsx
+++ b/data/planilla-ejemplo.xlsx
@@ -1752,7 +1752,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF303083"/>
+        <fgColor rgb="FF1A449E"/>
       </patternFill>
     </fill>
   </fills>
